--- a/unilabos/devices/eit_synthesis_station/sheet/batch_in_tray.xlsx
+++ b/unilabos/devices/eit_synthesis_station/sheet/batch_in_tray.xlsx
@@ -1,24 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Uni-Lab-OS\unilabos\devices\eit_synthesis_station\sheet\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D82356-8247-4779-89F3-7151EAAC8C43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="batch_in_tray"/>
-    <sheet r:id="rId2" sheetId="2" name="validation_meta"/>
+    <sheet name="batch_in_tray" sheetId="1" r:id="rId1"/>
+    <sheet name="validation_meta" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="tray_type_options">validation_meta!$A$1:$A$13</definedName>
   </definedNames>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+  <si>
+    <t>position</t>
+  </si>
+  <si>
+    <t>tray_type</t>
+  </si>
   <si>
     <t>2 mL反应试管托盘(201000726) [1-24]</t>
   </si>
@@ -59,39 +71,32 @@
     <t>125 mL试剂瓶托盘(220000023) [A1-A2]</t>
   </si>
   <si>
-    <t>position</t>
-  </si>
-  <si>
-    <t>tray_type</t>
-  </si>
-  <si>
     <t>content(耗材填数量; 物质填: A1|名称|2mL; B2|名称|5mg)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>TB-2-1</t>
-  </si>
-  <si>
-    <t>TB-2-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -102,14 +107,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -121,32 +119,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -157,10 +143,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -198,71 +184,69 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -286,53 +270,54 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
                 <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="51000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="94000"/>
+                <a:shade val="94000"/>
                 <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
-              <a:shade val="9500"/>
+              <a:shade val="95000"/>
               <a:satMod val="105000"/>
             </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -342,7 +327,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -351,7 +336,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -360,7 +345,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -368,10 +353,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -400,7 +385,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="20000"/>
+                <a:shade val="20000"/>
                 <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
@@ -413,12 +398,13 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
                 <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
+                <a:shade val="30000"/>
                 <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
@@ -436,133 +422,123 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="2" width="23.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="2" width="60.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="5" width="80.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="23.1796875" customWidth="1"/>
+    <col min="2" max="2" width="60" customWidth="1"/>
+    <col min="3" max="3" width="80" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
-      <c r="A1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="3" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="20.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="4">
-        <v>96</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="20.25">
-      <c r="A3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="4">
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2">
         <v>24</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="2">
+    <dataValidation type="list" sqref="A2:A101" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>"TB-1-1,TB-1-2,TB-1-3,TB-1-4,TB-2-1,TB-2-2,TB-2-3,TB-2-4,W-1-1,W-1-2,W-1-3,W-1-4,W-1-5,W-1-6,W-1-7,W-1-8"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showInputMessage="1" sqref="B2:B101" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>tray_type_options</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" style="2" width="12.43357142857143" customWidth="1" bestFit="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="17.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="17.25">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="17.25">
-      <c r="A3" s="1" t="s">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="17.25">
-      <c r="A4" s="1" t="s">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="17.25">
-      <c r="A5" s="1" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="17.25">
-      <c r="A6" s="1" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="17.25">
-      <c r="A7" s="1" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="17.25">
-      <c r="A8" s="1" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="17.25">
-      <c r="A9" s="1" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="17.25">
-      <c r="A10" s="1" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="17.25">
-      <c r="A11" s="1" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="17.25">
-      <c r="A12" s="1" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="17.25">
-      <c r="A13" s="1" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>12</v>
       </c>
     </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/unilabos/devices/eit_synthesis_station/sheet/batch_in_tray.xlsx
+++ b/unilabos/devices/eit_synthesis_station/sheet/batch_in_tray.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Uni-Lab-OS\unilabos\devices\eit_synthesis_station\sheet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fish/Documents/GitHub/Uni-Lab-OS/unilabos/devices/eit_synthesis_station/sheet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D82356-8247-4779-89F3-7151EAAC8C43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E03FD323-E414-0944-8B75-897C381F7128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="batch_in_tray" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <si>
     <t>position</t>
   </si>
@@ -32,6 +32,36 @@
     <t>tray_type</t>
   </si>
   <si>
+    <t>content</t>
+  </si>
+  <si>
+    <t>shelf_position</t>
+  </si>
+  <si>
+    <t>storage</t>
+  </si>
+  <si>
+    <t>TB-2-1</t>
+  </si>
+  <si>
+    <t>30 mL粉桶托盘(201000600)</t>
+  </si>
+  <si>
+    <t>3-1</t>
+  </si>
+  <si>
+    <t>对二甲胺基苯甲醛|3-2A;4-3;3,5-二甲氧基苯甲醛|4-3</t>
+  </si>
+  <si>
+    <t>TB-2-2</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>对苯基苯甲醛|4-3</t>
+  </si>
+  <si>
     <t>2 mL反应试管托盘(201000726) [1-24]</t>
   </si>
   <si>
@@ -71,11 +101,11 @@
     <t>125 mL试剂瓶托盘(220000023) [A1-A2]</t>
   </si>
   <si>
-    <t>content(耗材填数量; 物质填: A1|名称|2mL; B2|名称|5mg)</t>
+    <t>A1|对二甲胺基苯甲醛|2000mg;B1|3,5-二甲氧基苯甲醛|2000mg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>TB-2-1</t>
+    <t>A1|对苯基苯甲醛|2000mg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -83,7 +113,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -107,7 +137,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -115,12 +145,34 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -423,118 +475,174 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="23.1796875" customWidth="1"/>
-    <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="80" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="125.1640625" customWidth="1"/>
+    <col min="4" max="4" width="18.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="39" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" ht="15">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="31.5" customHeight="1">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2">
-        <v>24</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="39.5" customHeight="1">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="79" customHeight="1">
+      <c r="C4" s="3"/>
+      <c r="D4"/>
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="D5"/>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="D6"/>
+      <c r="E6" s="3"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="D7"/>
+      <c r="E7" s="3"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="D8"/>
+      <c r="E8" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="A2:A101" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="A2:A91" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"TB-1-1,TB-1-2,TB-1-3,TB-1-4,TB-2-1,TB-2-2,TB-2-3,TB-2-4,W-1-1,W-1-2,W-1-3,W-1-4,W-1-5,W-1-6,W-1-7,W-1-8"</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" sqref="B2:B101" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" showInputMessage="1" sqref="B2:B91" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>tray_type_options</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="64" orientation="landscape" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A13"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
